--- a/artfynd/A 25079-2026 artfynd.xlsx
+++ b/artfynd/A 25079-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124508735</v>
+        <v>124526789</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,14 +708,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -728,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569506</v>
+        <v>569517</v>
       </c>
       <c r="R2" t="n">
-        <v>6308841</v>
+        <v>6308865</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,12 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,77 +776,78 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Otto Bylén Claesson</t>
+          <t>Magnus Elfwing</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Otto Bylén Claesson</t>
+          <t>Magnus Elfwing</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124541284</v>
+        <v>124526787</v>
       </c>
       <c r="B3" t="n">
-        <v>56471</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rugstorp SV, Sm</t>
+          <t>Rugstorpsvägen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569540</v>
+        <v>569517</v>
       </c>
       <c r="R3" t="n">
-        <v>6308847</v>
+        <v>6308865</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,67 +874,71 @@
           <t>2025-04-28</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-28</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Sjödahl</t>
+          <t>Magnus Elfwing</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Sjödahl</t>
+          <t>Magnus Elfwing</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124526787</v>
+        <v>124508735</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,13 +946,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569517</v>
+        <v>569506</v>
       </c>
       <c r="R4" t="n">
-        <v>6308865</v>
+        <v>6308841</v>
       </c>
       <c r="S4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,33 +1005,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Elfwing</t>
+          <t>Otto Bylén Claesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Elfwing</t>
+          <t>Otto Bylén Claesson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124526789</v>
+        <v>124526785</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,16 +1035,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,11 +1057,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1129,6 +1130,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,12 +1152,7 @@
         <v>124541363</v>
       </c>
       <c r="B6" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,15 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124526785</v>
+        <v>124552379</v>
       </c>
       <c r="B7" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1297,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -1317,20 +1313,24 @@
           <t>frispringande/krypande</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rugstorpsvägen, Sm</t>
+          <t>Kyrkmossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569517</v>
+        <v>569504</v>
       </c>
       <c r="R7" t="n">
-        <v>6308865</v>
+        <v>6308836</v>
       </c>
       <c r="S7" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,34 +1378,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Elfwing</t>
+          <t>Carl Tamario</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Elfwing</t>
+          <t>Carl Tamario</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552379</v>
+        <v>124541284</v>
       </c>
       <c r="B8" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,62 +1407,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>208255</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kyrkmossen, Sm</t>
+          <t>Rugstorp SV, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569504</v>
+        <v>569540</v>
       </c>
       <c r="R8" t="n">
-        <v>6308836</v>
+        <v>6308847</v>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1492,22 +1466,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,18 +1480,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carl Tamario</t>
+          <t>Martin Sjödahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Tamario</t>
+          <t>Martin Sjödahl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 25079-2026 artfynd.xlsx
+++ b/artfynd/A 25079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124526789</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124526787</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124508735</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124526785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124541363</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1393,6 +1423,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124552379</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1496,8 +1531,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124541284</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>